--- a/artfynd/Alingsås artfynd.xlsx
+++ b/artfynd/Alingsås artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126380538</v>
+        <v>126380537</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677699</v>
+        <v>677709</v>
       </c>
       <c r="R2" t="n">
-        <v>7115926</v>
+        <v>7115905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,48 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>174990</v>
+        <v>126380536</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alingsås, Ås lm</t>
+          <t>Strand, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678645</v>
+        <v>677711</v>
       </c>
       <c r="R3" t="n">
-        <v>7114430</v>
+        <v>7115905</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-08-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-08-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,63 +869,78 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126380536</v>
+        <v>174990</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strand, Ås lm</t>
+          <t>Alingsås, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677711</v>
+        <v>678645</v>
       </c>
       <c r="R4" t="n">
-        <v>7115905</v>
+        <v>7114430</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2004-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2004-08-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,145 +981,18 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Pontus Wallén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>126380537</v>
-      </c>
-      <c r="B5" t="n">
-        <v>88654</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>510</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Strand, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>677709</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7115905</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
